--- a/resources/路网字段属性映射关系.xlsx
+++ b/resources/路网字段属性映射关系.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="12585" windowHeight="5730"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
     <t>OSM字段</t>
   </si>
   <si>
-    <t>isLink</t>
+    <t>渠道</t>
   </si>
   <si>
     <t>道路等级</t>

--- a/resources/路网字段属性映射关系.xlsx
+++ b/resources/路网字段属性映射关系.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="12585" windowHeight="5730"/>
+    <workbookView windowWidth="12825" windowHeight="6315"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="20">
   <si>
-    <t>OSM字段</t>
+    <t>OSM道路等级</t>
   </si>
   <si>
     <t>渠道</t>
